--- a/public/templates/aile_durumu_bildirimi.xlsx
+++ b/public/templates/aile_durumu_bildirimi.xlsx
@@ -504,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -559,130 +559,133 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -724,86 +727,86 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1142,153 +1145,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="79" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="42.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="97" t="s">
+      <c r="A2" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="91" t="s">
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="45"/>
+      <c r="N2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="93"/>
-      <c r="S2" s="94"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="95"/>
-      <c r="W2" s="95"/>
-      <c r="X2" s="96"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="42"/>
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="1:25" s="9" customFormat="1" ht="27.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="19"/>
+      <c r="B3" s="90"/>
       <c r="C3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="83" t="s">
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="22" t="s">
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="20" t="s">
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="21"/>
+      <c r="W3" s="92"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="90"/>
       <c r="C4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="29" t="s">
+      <c r="D4" s="94"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="95"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="97" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="30"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="35"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="19"/>
       <c r="Y4" s="4"/>
     </row>
     <row r="5" spans="1:25" s="9" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
+      <c r="A5" s="91"/>
+      <c r="B5" s="92"/>
       <c r="C5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="87"/>
+      <c r="E5" s="34"/>
       <c r="F5" s="12"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="10"/>
-      <c r="J5" s="87" t="s">
+      <c r="J5" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="87"/>
+      <c r="K5" s="34"/>
       <c r="L5" s="12"/>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
@@ -1297,532 +1300,616 @@
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
       <c r="S5" s="11"/>
-      <c r="T5" s="52" t="s">
+      <c r="T5" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="U5" s="54"/>
+      <c r="U5" s="36"/>
       <c r="V5" s="7"/>
       <c r="W5" s="10"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="4"/>
     </row>
     <row r="6" spans="1:25" s="9" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="41"/>
-      <c r="L6" s="41"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="39"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="39"/>
-      <c r="X6" s="42"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="78"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="52"/>
+      <c r="N6" s="52"/>
+      <c r="O6" s="52"/>
+      <c r="P6" s="52"/>
+      <c r="Q6" s="52"/>
+      <c r="R6" s="52"/>
+      <c r="S6" s="52"/>
+      <c r="T6" s="52"/>
+      <c r="U6" s="52"/>
+      <c r="V6" s="53"/>
+      <c r="W6" s="52"/>
+      <c r="X6" s="54"/>
       <c r="Y6" s="4"/>
     </row>
     <row r="7" spans="1:25" s="9" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="80"/>
       <c r="D7" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="45" t="s">
+      <c r="E7" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="45"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="45"/>
-      <c r="O7" s="45"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="43" t="s">
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="74"/>
+      <c r="O7" s="74"/>
+      <c r="P7" s="75"/>
+      <c r="Q7" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="R7" s="44"/>
-      <c r="S7" s="44"/>
-      <c r="T7" s="44"/>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="47"/>
+      <c r="R7" s="80"/>
+      <c r="S7" s="80"/>
+      <c r="T7" s="80"/>
+      <c r="U7" s="80"/>
+      <c r="V7" s="80"/>
+      <c r="W7" s="80"/>
+      <c r="X7" s="81"/>
       <c r="Y7" s="4"/>
     </row>
     <row r="8" spans="1:25" s="9" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="48"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="50" t="s">
+      <c r="A8" s="82"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52" t="s">
+      <c r="F8" s="85"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="53"/>
-      <c r="J8" s="52" t="s">
+      <c r="I8" s="87"/>
+      <c r="J8" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="53"/>
-      <c r="L8" s="52" t="s">
+      <c r="K8" s="87"/>
+      <c r="L8" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="M8" s="54"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="34"/>
-      <c r="X8" s="55"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="87"/>
+      <c r="Q8" s="82"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="48"/>
+      <c r="X8" s="49"/>
       <c r="Y8" s="4"/>
     </row>
     <row r="9" spans="1:25" s="9" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="25"/>
+      <c r="A9" s="83"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="100"/>
+      <c r="O9" s="100"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="83"/>
+      <c r="R9" s="84"/>
+      <c r="S9" s="84"/>
+      <c r="T9" s="84"/>
+      <c r="U9" s="84"/>
+      <c r="V9" s="84"/>
+      <c r="W9" s="84"/>
+      <c r="X9" s="88"/>
       <c r="Y9" s="4"/>
     </row>
     <row r="10" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="39"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="39"/>
-      <c r="P10" s="39"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="39"/>
-      <c r="S10" s="39"/>
-      <c r="T10" s="39"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="39"/>
-      <c r="W10" s="39"/>
-      <c r="X10" s="42"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="53"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="52"/>
+      <c r="M10" s="52"/>
+      <c r="N10" s="52"/>
+      <c r="O10" s="52"/>
+      <c r="P10" s="52"/>
+      <c r="Q10" s="52"/>
+      <c r="R10" s="52"/>
+      <c r="S10" s="52"/>
+      <c r="T10" s="52"/>
+      <c r="U10" s="52"/>
+      <c r="V10" s="52"/>
+      <c r="W10" s="52"/>
+      <c r="X10" s="54"/>
       <c r="Y10" s="4"/>
     </row>
     <row r="11" spans="1:25" s="9" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="56" t="s">
+      <c r="A11" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="57"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="60" t="s">
+      <c r="B11" s="56"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="56" t="s">
+      <c r="E11" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F11" s="58"/>
-      <c r="G11" s="62" t="s">
+      <c r="F11" s="57"/>
+      <c r="G11" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="H11" s="63"/>
-      <c r="I11" s="56" t="s">
+      <c r="H11" s="64"/>
+      <c r="I11" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="58"/>
-      <c r="K11" s="60" t="s">
+      <c r="J11" s="57"/>
+      <c r="K11" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="66" t="s">
+      <c r="L11" s="67" t="s">
         <v>32</v>
       </c>
-      <c r="M11" s="67"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="80" t="s">
+      <c r="M11" s="68"/>
+      <c r="N11" s="69"/>
+      <c r="O11" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="P11" s="81"/>
-      <c r="Q11" s="81"/>
-      <c r="R11" s="81"/>
-      <c r="S11" s="81"/>
-      <c r="T11" s="81"/>
-      <c r="U11" s="81"/>
-      <c r="V11" s="81"/>
-      <c r="W11" s="81"/>
-      <c r="X11" s="82"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="30"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="30"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="30"/>
+      <c r="X11" s="31"/>
       <c r="Y11" s="4"/>
     </row>
     <row r="12" spans="1:25" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="36"/>
+      <c r="A12" s="58"/>
       <c r="B12" s="59"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="65"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="69"/>
-      <c r="M12" s="70"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="72" t="s">
+      <c r="C12" s="60"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="70"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="72"/>
+      <c r="O12" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="P12" s="45"/>
-      <c r="Q12" s="46"/>
-      <c r="R12" s="72" t="s">
+      <c r="P12" s="74"/>
+      <c r="Q12" s="75"/>
+      <c r="R12" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="S12" s="45"/>
-      <c r="T12" s="46"/>
-      <c r="U12" s="72" t="s">
+      <c r="S12" s="74"/>
+      <c r="T12" s="75"/>
+      <c r="U12" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="V12" s="46"/>
-      <c r="W12" s="73" t="s">
+      <c r="V12" s="75"/>
+      <c r="W12" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="X12" s="74"/>
+      <c r="X12" s="77"/>
       <c r="Y12" s="4"/>
     </row>
     <row r="13" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="32"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="35"/>
+      <c r="A13" s="18"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="35"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="19"/>
       <c r="K13" s="8"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="32"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="35"/>
-      <c r="U13" s="89"/>
-      <c r="V13" s="90"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="35"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="18"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="18"/>
+      <c r="X13" s="19"/>
       <c r="Y13" s="4"/>
     </row>
     <row r="14" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="32"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="35"/>
+      <c r="A14" s="18"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="35"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="19"/>
       <c r="K14" s="8"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="32"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="32"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="89"/>
-      <c r="V14" s="90"/>
-      <c r="W14" s="32"/>
-      <c r="X14" s="35"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="18"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="19"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="18"/>
+      <c r="X14" s="19"/>
       <c r="Y14" s="4"/>
     </row>
     <row r="15" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="32"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="35"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="19"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="35"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="19"/>
       <c r="K15" s="8"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="89"/>
-      <c r="V15" s="90"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="35"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="19"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="19"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="19"/>
       <c r="Y15" s="4"/>
     </row>
     <row r="16" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="32"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="35"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="35"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="35"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="35"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="19"/>
       <c r="K16" s="8"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="89"/>
-      <c r="V16" s="90"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="35"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="19"/>
+      <c r="R16" s="18"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="19"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="18"/>
+      <c r="X16" s="19"/>
       <c r="Y16" s="4"/>
     </row>
     <row r="17" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="32"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="35"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="19"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="35"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
       <c r="K17" s="8"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="35"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="89"/>
-      <c r="V17" s="90"/>
-      <c r="W17" s="32"/>
-      <c r="X17" s="35"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="19"/>
+      <c r="R17" s="18"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="18"/>
+      <c r="X17" s="19"/>
       <c r="Y17" s="4"/>
     </row>
     <row r="18" spans="1:25" s="9" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="76" t="s">
+      <c r="A18" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="34"/>
-      <c r="W18" s="34"/>
-      <c r="X18" s="55"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="48"/>
+      <c r="O18" s="48"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="48"/>
+      <c r="V18" s="48"/>
+      <c r="W18" s="48"/>
+      <c r="X18" s="49"/>
       <c r="Y18" s="4"/>
     </row>
     <row r="19" spans="1:25" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="85" t="s">
+      <c r="A19" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="49"/>
-      <c r="J19" s="49"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="49"/>
-      <c r="M19" s="49"/>
-      <c r="N19" s="49"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="49"/>
-      <c r="Q19" s="49"/>
-      <c r="R19" s="49"/>
-      <c r="S19" s="49"/>
-      <c r="T19" s="49"/>
-      <c r="U19" s="88" t="s">
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="22"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
+      <c r="T19" s="22"/>
+      <c r="U19" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="V19" s="88"/>
-      <c r="W19" s="86"/>
-      <c r="X19" s="86"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
       <c r="Y19" s="4"/>
     </row>
     <row r="20" spans="1:25" s="9" customFormat="1" ht="65.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="86"/>
-      <c r="N20" s="86"/>
-      <c r="O20" s="86"/>
-      <c r="P20" s="86"/>
-      <c r="Q20" s="86"/>
-      <c r="R20" s="86"/>
-      <c r="S20" s="86"/>
-      <c r="T20" s="86"/>
-      <c r="U20" s="86"/>
-      <c r="V20" s="86"/>
-      <c r="W20" s="86"/>
-      <c r="X20" s="86"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="21"/>
+      <c r="R20" s="21"/>
+      <c r="S20" s="21"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+      <c r="V20" s="21"/>
+      <c r="W20" s="21"/>
+      <c r="X20" s="21"/>
       <c r="Y20" s="4"/>
     </row>
     <row r="21" spans="1:25" ht="99.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="77"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="77"/>
-      <c r="L21" s="77"/>
-      <c r="M21" s="77"/>
-      <c r="N21" s="77"/>
-      <c r="O21" s="77"/>
-      <c r="P21" s="77"/>
-      <c r="Q21" s="77"/>
-      <c r="R21" s="77"/>
-      <c r="S21" s="77"/>
-      <c r="T21" s="77"/>
-      <c r="U21" s="77"/>
-      <c r="V21" s="77"/>
-      <c r="W21" s="77"/>
-      <c r="X21" s="77"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="50"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="50"/>
+      <c r="T21" s="50"/>
+      <c r="U21" s="50"/>
+      <c r="V21" s="50"/>
+      <c r="W21" s="50"/>
+      <c r="X21" s="50"/>
       <c r="Y21" s="5"/>
     </row>
     <row r="22" spans="1:25" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="75"/>
-      <c r="C22" s="75"/>
-      <c r="D22" s="75"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
-      <c r="J22" s="75"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="75"/>
-      <c r="M22" s="75"/>
-      <c r="N22" s="75"/>
-      <c r="O22" s="75"/>
-      <c r="P22" s="75"/>
-      <c r="Q22" s="75"/>
-      <c r="R22" s="75"/>
-      <c r="S22" s="75"/>
-      <c r="T22" s="75"/>
-      <c r="U22" s="75"/>
-      <c r="V22" s="75"/>
-      <c r="W22" s="75"/>
-      <c r="X22" s="75"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="46"/>
+      <c r="O22" s="46"/>
+      <c r="P22" s="46"/>
+      <c r="Q22" s="46"/>
+      <c r="R22" s="46"/>
+      <c r="S22" s="46"/>
+      <c r="T22" s="46"/>
+      <c r="U22" s="46"/>
+      <c r="V22" s="46"/>
+      <c r="W22" s="46"/>
+      <c r="X22" s="46"/>
       <c r="Y22" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="100">
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:P9"/>
+    <mergeCell ref="A3:B5"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="D4:L4"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="W12:X12"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="A6:X6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="E7:P7"/>
+    <mergeCell ref="Q7:X7"/>
+    <mergeCell ref="A8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:P8"/>
+    <mergeCell ref="Q8:X9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="G11:H12"/>
+    <mergeCell ref="I11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:N12"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A22:X22"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="A18:X18"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="A21:X21"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:X20"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:X1"/>
+    <mergeCell ref="O11:X11"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="N2:R2"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A10:X10"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:F12"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:T16"/>
     <mergeCell ref="W14:X14"/>
     <mergeCell ref="W13:X13"/>
     <mergeCell ref="U19:V19"/>
@@ -1839,90 +1926,6 @@
     <mergeCell ref="G15:H15"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="L15:N15"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:X1"/>
-    <mergeCell ref="O11:X11"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A22:X22"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="A18:X18"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="A21:X21"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:X20"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A10:X10"/>
-    <mergeCell ref="A11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:F12"/>
-    <mergeCell ref="G11:H12"/>
-    <mergeCell ref="I11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:N12"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="R12:T12"/>
-    <mergeCell ref="W12:X12"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="A6:X6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="E7:P7"/>
-    <mergeCell ref="Q7:X7"/>
-    <mergeCell ref="A8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:P8"/>
-    <mergeCell ref="Q8:X9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:P9"/>
-    <mergeCell ref="A3:B5"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="S3:U3"/>
-    <mergeCell ref="D4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="V3:W3"/>
   </mergeCells>
   <pageMargins left="0.43" right="0.2" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" r:id="rId1"/>
